--- a/Archivos_Compartidos/Cartas de confirmación/20250821/Banorte/CamposExtraer.xlsx
+++ b/Archivos_Compartidos/Cartas de confirmación/20250821/Banorte/CamposExtraer.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Archivos_Compartidos\Cartas de confirmación\20250821\Banorte\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SAMMX\Documents\GitHub\SAM_Santander\Archivos_Compartidos\Cartas de confirmación\20250821\Banorte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1DE13B94-9AC1-4E18-9FC8-E9EA0DAEADD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F57461C-148D-4B02-91C9-3A2F9A8EA93A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5B73482C-0A2A-48EB-AAB4-00D748B4A503}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5B73482C-0A2A-48EB-AAB4-00D748B4A503}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>Contraparte</t>
   </si>
@@ -77,22 +77,34 @@
     <t>BANORTE</t>
   </si>
   <si>
-    <t>2U</t>
-  </si>
-  <si>
-    <t>CBIC002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  1,499,999,891.55 </t>
-  </si>
-  <si>
-    <t>LF</t>
-  </si>
-  <si>
-    <t>BONDESF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  2,499,999,983.02 </t>
+    <t xml:space="preserve">Contrato de inversión </t>
+  </si>
+  <si>
+    <t>Cliente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primero dijitos de Emisora antes del primer guion bajo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primero dijitos de Emisora antes del segundo guion bajo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primero dijitos de Emisora despues del segundo guion bajo </t>
+  </si>
+  <si>
+    <t>Tasa contratada - Sin el signo de %</t>
+  </si>
+  <si>
+    <t>Títulos</t>
+  </si>
+  <si>
+    <t>Precio- Sin el signo de precios.</t>
+  </si>
+  <si>
+    <t>Monto</t>
+  </si>
+  <si>
+    <t>Fecha instrucción</t>
   </si>
 </sst>
 </file>
@@ -518,9 +530,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EB283FA-E207-442A-B99F-A49836BAE511}">
   <dimension ref="A1:L4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="46" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -558,79 +576,59 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="4">
-        <v>500092291</v>
-      </c>
-      <c r="C2" s="5"/>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="D2" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="4">
-        <v>300117</v>
-      </c>
-      <c r="G2" s="4">
-        <v>7.51</v>
-      </c>
-      <c r="H2" s="6">
-        <v>1562504</v>
-      </c>
-      <c r="I2" s="4">
-        <v>959.99747300000001</v>
-      </c>
-      <c r="J2" s="4">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" s="7">
-        <v>45889</v>
+        <v>21</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="4">
-        <v>57253852</v>
-      </c>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
       <c r="C3" s="5"/>
-      <c r="D3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="4">
-        <v>280420</v>
-      </c>
-      <c r="G3" s="4">
-        <v>7.76</v>
-      </c>
-      <c r="H3" s="6">
-        <v>25084985</v>
-      </c>
-      <c r="I3" s="4">
-        <v>99.661210999999994</v>
-      </c>
-      <c r="J3" s="4">
-        <v>1</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="7">
-        <v>45889</v>
-      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="7"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
     </row>
   </sheetData>
